--- a/InsectAI CRediT register.xlsx
+++ b/InsectAI CRediT register.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://naturalhistorymuseum.sharepoint.com/sites/EducationNatureParkProgramme/Shared Documents/Community Science incl digital tools/5. Research planning and data analysis/Insect AI COST Action/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="13_ncr:1_{9805CE59-76B2-4068-B5DB-F15CA8DEEF50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71AFAC39-AA12-4299-9145-34B110E1C287}"/>
+  <xr:revisionPtr revIDLastSave="108" documentId="13_ncr:1_{9805CE59-76B2-4068-B5DB-F15CA8DEEF50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71843082-4492-4F27-819D-36DFDF213D28}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="352" activeTab="1" xr2:uid="{4C054703-C80A-4328-B0BE-C3D095480D7D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="352" activeTab="2" xr2:uid="{4C054703-C80A-4328-B0BE-C3D095480D7D}"/>
   </bookViews>
   <sheets>
-    <sheet name="CRediT Definitions" sheetId="3" r:id="rId1"/>
-    <sheet name="Contributors" sheetId="1" r:id="rId2"/>
+    <sheet name="README" sheetId="4" r:id="rId1"/>
+    <sheet name="CRediT Definitions" sheetId="3" r:id="rId2"/>
+    <sheet name="Contributors" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'CRediT Definitions'!$A$7:$B$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CRediT Definitions'!$A$7:$B$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="59">
   <si>
     <t>Conceptualization</t>
   </si>
@@ -190,13 +191,55 @@
   </si>
   <si>
     <t>J</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>How to Use the Spreadsheet</t>
+  </si>
+  <si>
+    <t>Adding a New Individual</t>
+  </si>
+  <si>
+    <t>Updating an Individual</t>
+  </si>
+  <si>
+    <t>Version Control Guidance</t>
+  </si>
+  <si>
+    <t>This spreadsheet is used to track contributions to the InsectAI COST Action using the CRediT typology (https://credit.niso.org). It provides a single-row-per-person layout with role selection via dropdown boxes.</t>
+  </si>
+  <si>
+    <t>The spreadsheet enables us to:
+Record participant names and associated roles
+Capture multiple roles per person in a consistent, controlled format
+Maintain a transparent, version-controlled history of credit changes through GitHub</t>
+  </si>
+  <si>
+    <t>1. Insert a new row in the main table.
+2. Enter the participant’s title, name, institution, and ORCID (if applicable).
+3. Select relevant roles within the COST Action using the dropdown boxes (see the CRediT Definitions sheet for explanations of each role).
+4. Add any additional information in the Contribution Details column.</t>
+  </si>
+  <si>
+    <t>1. Locate the individual in the table.
+2. Update personal details as needed.
+3. Add or remove roles using the dropdown boxes.
+4. Update contribution details if required.</t>
+  </si>
+  <si>
+    <t>Because Excel files are binary, please follow these practices to minimise merge conflicts:
+Make changes in small, clear commits.
+Avoid editing the same rows as someone else simultaneously.
+Use descriptive commit messages (e.g., "Added roles for Dr A. Smith").</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,6 +271,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16.5"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13.75"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -250,7 +317,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -269,26 +336,42 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -330,7 +413,6 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B8178FF4-D7AA-4EF7-A351-3F823F143BAB}" name="Table3" displayName="Table3" ref="A1:U4" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:U4" xr:uid="{B8178FF4-D7AA-4EF7-A351-3F823F143BAB}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{17C15E88-DBE9-40A8-80F1-E1E3228CF3D0}" name="Title"/>
     <tableColumn id="2" xr3:uid="{748815AD-C68B-4121-9EEE-46385F0AD8FA}" name="First name"/>
@@ -674,26 +756,104 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{888CC82D-EFAC-498A-921B-89C9F553618E}">
+  <dimension ref="A1:A14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="187.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="25.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="60" x14ac:dyDescent="0.3">
+      <c r="A4" s="14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="25.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="60" x14ac:dyDescent="0.3">
+      <c r="A7" s="16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A8" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="60" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="25.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="60" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A12" s="16"/>
+    </row>
+    <row r="13" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A13" s="16"/>
+    </row>
+    <row r="14" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A14" s="16"/>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3880193-C118-44EC-B023-447664153FDA}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="95.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="95.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:3" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A1" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>30</v>
       </c>
@@ -701,17 +861,17 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" s="7"/>
     </row>
-    <row r="5" spans="1:3" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:3" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="9"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B5" s="12"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
@@ -719,7 +879,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -727,7 +887,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
@@ -735,7 +895,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
@@ -743,7 +903,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
@@ -751,7 +911,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>4</v>
       </c>
@@ -759,7 +919,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>5</v>
       </c>
@@ -767,7 +927,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>6</v>
       </c>
@@ -775,7 +935,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>7</v>
       </c>
@@ -783,7 +943,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>8</v>
       </c>
@@ -791,7 +951,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>9</v>
       </c>
@@ -799,7 +959,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>10</v>
       </c>
@@ -807,7 +967,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>11</v>
       </c>
@@ -815,7 +975,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>12</v>
       </c>
@@ -823,7 +983,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>13</v>
       </c>
@@ -832,6 +992,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:B5"/>
@@ -844,87 +1005,87 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6DC2CA-E426-46ED-A29E-DB1A8DD372C0}">
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="24.36328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="24.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="47.08984375" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.90625" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="20" width="5.6328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="55.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="20" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="55.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="14" customFormat="1" ht="120" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:21" s="10" customFormat="1" ht="118.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="12" t="s">
+      <c r="P1" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="Q1" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="R1" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="S1" s="12" t="s">
+      <c r="S1" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="T1" s="13" t="s">
+      <c r="T1" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="U1" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>46</v>
       </c>
@@ -951,6 +1112,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:T1048576" xr:uid="{0F7D6B94-B467-43FB-8B17-6E55D0BF9CC7}">
       <formula1>"x"</formula1>
@@ -965,6 +1127,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A965D94F0762894DBFBF8132F36DD753" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2e5e294aee1e8b15d1ef8ee2be4d20ba">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="01a464aa-a786-405b-bb6b-b90e04698418" xmlns:ns3="37c47d49-5c3e-4564-83ee-3a7de24ace65" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="74ad2e1e60d70087ea82dab5b61f0c8d" ns2:_="" ns3:_="">
     <xsd:import namespace="01a464aa-a786-405b-bb6b-b90e04698418"/>
@@ -1229,15 +1400,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1253,6 +1415,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AAE77EC-DAF1-4B78-88D6-A3A6D6E12249}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D965612-6479-4472-860E-9EF9F9A3747A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1267,14 +1437,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AAE77EC-DAF1-4B78-88D6-A3A6D6E12249}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
